--- a/Questions.xlsx
+++ b/Questions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\personal\tyro-study\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0367E68F-25FF-40F1-8C0A-897ABD2C99C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48EE11A3-92A0-4604-95F9-BD084535C3F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8C830F93-8377-4CF9-80AE-B87DB3F8D0C2}"/>
   </bookViews>
@@ -44,18 +44,6 @@
     <t>Question</t>
   </si>
   <si>
-    <t>Option 1</t>
-  </si>
-  <si>
-    <t>Option 2</t>
-  </si>
-  <si>
-    <t>Option 3</t>
-  </si>
-  <si>
-    <t>Option 4</t>
-  </si>
-  <si>
     <t>Answer</t>
   </si>
   <si>
@@ -75,6 +63,18 @@
   </si>
   <si>
     <t>web host provider</t>
+  </si>
+  <si>
+    <t>Answer1</t>
+  </si>
+  <si>
+    <t>Answer2</t>
+  </si>
+  <si>
+    <t>Answer3</t>
+  </si>
+  <si>
+    <t>Answer4</t>
   </si>
 </sst>
 </file>
@@ -461,39 +461,39 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="G1" t="s">
         <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
         <v>7</v>
-      </c>
-      <c r="B2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" t="s">
-        <v>11</v>
       </c>
       <c r="F2">
         <v>1</v>
